--- a/data/trans_dic/IP31KM07_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM07_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>90,38%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,16; 95,25</t>
+          <t>81,58; 94,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,49; 92,44</t>
+          <t>86,55; 95,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,47; 92,17</t>
+          <t>86,05; 93,65</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,32; 95,62</t>
+          <t>81,24; 92,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,73; 91,5</t>
+          <t>89,03; 95,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,35; 92,46</t>
+          <t>86,94; 93,02</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,51; 87,55</t>
+          <t>75,17; 89,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>76,98; 90,53</t>
+          <t>78,59; 90,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,12; 86,74</t>
+          <t>79,12; 88,14</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,46; 94,89</t>
+          <t>84,92; 93,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,1; 93,55</t>
+          <t>87,0; 94,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,52; 93,24</t>
+          <t>87,33; 93,24</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,71; 91,28</t>
+          <t>84,85; 90,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,68; 89,68</t>
+          <t>88,14; 92,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,77; 89,15</t>
+          <t>87,15; 90,82</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>174</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>104416</t>
+          <t>109498</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>116852</t>
+          <t>108774</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221268</t>
+          <t>218272</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98440; 108820</t>
+          <t>100261; 116117</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>99183; 126466</t>
+          <t>102652; 113258</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199530; 231402</t>
+          <t>207816; 226152</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>248</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>173080</t>
+          <t>205057</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>216604</t>
+          <t>167628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389684</t>
+          <t>372684</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>166231; 177969</t>
+          <t>187856; 213577</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>197344; 226484</t>
+          <t>160781; 172687</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>370118; 400923</t>
+          <t>358043; 383083</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>138428</t>
+          <t>139560</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>155196</t>
+          <t>132480</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293625</t>
+          <t>272040</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80024; 164807</t>
+          <t>125168; 149493</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>140945; 165751</t>
+          <t>121843; 139703</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215812; 322100</t>
+          <t>254410; 283426</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>216</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>150905</t>
+          <t>149237</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>159319</t>
+          <t>150062</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310224</t>
+          <t>299299</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>143890; 156105</t>
+          <t>141114; 154982</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>150893; 165869</t>
+          <t>142669; 154992</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>299174; 318715</t>
+          <t>288328; 307830</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>830</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>566831</t>
+          <t>603352</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>558945</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1214801</t>
+          <t>1162296</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>481405; 596171</t>
+          <t>582763; 619772</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>623159; 667911</t>
+          <t>544874; 570790</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1129051; 1246222</t>
+          <t>1137367; 1185217</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM07_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM07_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman legumbres más de una vez a la semana (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>89,1%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>90,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>81,58; 94,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>86,55; 95,5</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>86,05; 93,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>88,68%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>81,24; 92,36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>89,03; 95,62</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>86,94; 93,02</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>85,45%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>75,17; 89,77</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>78,59; 90,11</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>79,12; 88,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>89,81%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>91,51%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>90,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>84,92; 93,27</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>87,0; 94,52</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>87,33; 93,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>87,85%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>84,85; 90,24</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>88,14; 92,33</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>87,15; 90,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8909782575285988</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9171692890230205</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.903840669209041</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>109498</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>108774</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>218272</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.8158215932685121</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8655426946806791</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8605428038113836</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>100261; 116117</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>102652; 113258</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>207816; 226152</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9448422667364793</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9549767993991575</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.936469178498564</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8867661556918892</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9282114042379211</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9049402886289156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>205057</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>167628</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>372684</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8123824852503586</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8902958147536358</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8693891057604473</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>187856; 213577</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>160781; 172687</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>358043; 383083</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9236130199505134</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9562214821683853</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9301902933575804</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8380889087780468</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8545004183415106</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8460016177518865</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>139560</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>132480</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>272040</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7516627908284924</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7858886150957169</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.7911747011113611</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>125168; 149493</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121843; 139703</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>254410; 283426</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8977384568098015</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9010911255985073</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8814084876995747</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8981257020392633</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.915128166589748</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9065706452930022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>149237</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>150062</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>299299</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8492417787549223</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8700449151289398</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8733391070987097</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>141114; 154982</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142669; 154992</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>288328; 307830</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9326979331008985</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9451966307103767</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9324117857932244</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1672</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8784661877081333</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9041370287362955</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.890626746867701</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>603352</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>558945</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1162296</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8484900358767513</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8813762514338412</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8715245833372017</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>582763; 619772</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>544874; 570790</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1137367; 1185217</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9023731598603605</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9232969367772014</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9081909304307036</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman legumbres más de una vez a la semana (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>174</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>109498</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>108774</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>218272</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>100261</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>102652</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>207816</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>116117</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>113258</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>226152</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>291</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>248</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>205057</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>167628</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>372684</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>187856</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>160781</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>358043</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>213577</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>172687</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>383083</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>192</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>139560</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>132480</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>272040</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>125168</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>121843</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>254410</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>149493</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>139703</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>283426</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>149237</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>150062</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>299299</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>141114</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>142669</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>288328</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>154982</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>154992</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>307830</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>842</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>830</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>603352</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>558945</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1162296</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>582763</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>544874</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1137367</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>619772</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>570790</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1185217</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>